--- a/results/greedy/UAVs10_GRID13/tour/UAVs10_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs10_GRID13/tour/UAVs10_GRID13_1920_16_Greedy_sequences.xlsx
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02487262495560572</v>
+        <v>0.02230304200202227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01607387501280755</v>
+        <v>0.01524516701465473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02190108399372548</v>
+        <v>0.02101450000191107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02276754099875689</v>
+        <v>0.02169699996011332</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0201713340356946</v>
+        <v>0.02075562498066574</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01899249997222796</v>
+        <v>0.01765820803120732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02752145897829905</v>
+        <v>0.02532129199244082</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02598862501326948</v>
+        <v>0.02485987503314391</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02517437498318031</v>
+        <v>0.02388074999907985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02621787501266226</v>
+        <v>0.02512662502704188</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01898375002201647</v>
+        <v>0.01756608398864046</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02211495797382668</v>
+        <v>0.02076962502906099</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02580291696358472</v>
+        <v>0.0242477499996312</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02650845801690593</v>
+        <v>0.02482474996941164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02401491702767089</v>
+        <v>0.02276379195973277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02606345800450072</v>
+        <v>0.02471716701984406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02492595801595598</v>
+        <v>0.02419145795283839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02445229195291176</v>
+        <v>0.02319466701010242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02217554196249694</v>
+        <v>0.02121074998285621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0231446250109002</v>
+        <v>0.0219158330000937</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02299558295635507</v>
+        <v>0.02151958300964907</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02462745900265872</v>
+        <v>0.02316970902029425</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02023633400676772</v>
+        <v>0.01877462497213855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02053620800143108</v>
+        <v>0.01930408301996067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02377291698940098</v>
+        <v>0.02280908398097381</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02336012502200902</v>
+        <v>0.02254720800556242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01976195798488334</v>
+        <v>0.01857804198516533</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01706183404894546</v>
+        <v>0.01582733303075656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0222502090036869</v>
+        <v>0.02214862499386072</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01980033301515505</v>
+        <v>0.01897899998584762</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02146920800441876</v>
+        <v>0.02079366601537913</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02360175002831966</v>
+        <v>0.02191616699565202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02239658398320898</v>
+        <v>0.02141124999616295</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02377324999542907</v>
+        <v>0.02213858300819993</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02197170897852629</v>
+        <v>0.02097908401628956</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02205049997428432</v>
+        <v>0.0209497920004651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02152416598983109</v>
+        <v>0.02028662501834333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02428645797772333</v>
+        <v>0.02301929204259068</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01963533298112452</v>
+        <v>0.01871475001098588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0204821249935776</v>
+        <v>0.01889795798342675</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0232595830457285</v>
+        <v>0.02177158300764859</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02867579198209569</v>
+        <v>0.02719833300216123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02293900004588068</v>
+        <v>0.02228191698668525</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02503058302681893</v>
+        <v>0.02361233299598098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02183662500465289</v>
+        <v>0.02119599998695776</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02400249999482185</v>
+        <v>0.02298770798370242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02797741699032485</v>
+        <v>0.02658325002994388</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0240746249910444</v>
+        <v>0.0229863750282675</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02602408296661451</v>
+        <v>0.02574675000505522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02077158400788903</v>
+        <v>0.01962199999252334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.024859374971129</v>
+        <v>0.02411025000037625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02110195800196379</v>
+        <v>0.02132966701174155</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0184630419826135</v>
+        <v>0.01805799995781854</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02644566597882658</v>
+        <v>0.02581687504425645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02056374994572252</v>
+        <v>0.02035025000805035</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02408000000286847</v>
+        <v>0.02313479199074209</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02530466701136902</v>
+        <v>0.02394983300473541</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02045362500939518</v>
+        <v>0.01920141698792577</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02319508302025497</v>
+        <v>0.02192566700978205</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02218508295482025</v>
+        <v>0.0207838750211522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02411266596755013</v>
+        <v>0.02363608300220221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02240820799488574</v>
+        <v>0.02214041701517999</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02540770900668576</v>
+        <v>0.02520279202144593</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02363858296303079</v>
+        <v>0.02308645902667195</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.022241958999075</v>
+        <v>0.02163783396827057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02139987499685958</v>
+        <v>0.02069391700206324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01837345800595358</v>
+        <v>0.01783550000982359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01840633299434558</v>
+        <v>0.01782000000821427</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02440749999368563</v>
+        <v>0.02389599999878556</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02328529203077778</v>
+        <v>0.02301162498770282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02184420800767839</v>
+        <v>0.02160929096862674</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02228462498169392</v>
+        <v>0.02238254103576764</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0237378750462085</v>
+        <v>0.02262879197951406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01874737499747425</v>
+        <v>0.01792274997569621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02017366595100611</v>
+        <v>0.01948766701389104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02399575000163168</v>
+        <v>0.0230927910306491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02127004199428484</v>
+        <v>0.02011241699801758</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02134787500835955</v>
+        <v>0.02072425000369549</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02544704201864079</v>
+        <v>0.02383183303754777</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02624487498542294</v>
+        <v>0.02577712503261864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01990358298644423</v>
+        <v>0.01987350004492328</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02116862504044548</v>
+        <v>0.02084308303892612</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02397262497106567</v>
+        <v>0.02330608404008672</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02783450001152232</v>
+        <v>0.02708154200809076</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02278220799053088</v>
+        <v>0.02207716699922457</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02308029198320583</v>
+        <v>0.02187208301620558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02060237503610551</v>
+        <v>0.01924824999878183</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02207566704601049</v>
+        <v>0.0210511659970507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0292832909617573</v>
+        <v>0.02761712501524016</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02637683297507465</v>
+        <v>0.02454629103885964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0179342920309864</v>
+        <v>0.01717033400200307</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02380733302561566</v>
+        <v>0.02321916696382686</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02238995797233656</v>
+        <v>0.02176604204578325</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02049320901278406</v>
+        <v>0.0201610840158537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01791258295997977</v>
+        <v>0.01815995801007375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01877608295762911</v>
+        <v>0.01874537504045293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02821987500647083</v>
+        <v>0.02785629098070785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.026158457971178</v>
+        <v>0.025851208018139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02252012502867728</v>
+        <v>0.02232058299705386</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02152850001584738</v>
+        <v>0.02167058299528435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/results/greedy/UAVs10_GRID13/tour/UAVs10_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/greedy/UAVs10_GRID13/tour/UAVs10_GRID13_1920_16_Greedy_sequences.xlsx
@@ -632,7 +632,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02230304200202227</v>
+        <v>0.0228276249836199</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01524516701465473</v>
+        <v>0.01510970795061439</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02101450000191107</v>
+        <v>0.02123937499709427</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02169699996011332</v>
+        <v>0.02133658301318064</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02075562498066574</v>
+        <v>0.01915641705272719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01765820803120732</v>
+        <v>0.01747616700595245</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02532129199244082</v>
+        <v>0.02523191599175334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02485987503314391</v>
+        <v>0.02416158397682011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02388074999907985</v>
+        <v>0.02344716695370153</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02512662502704188</v>
+        <v>0.02472437504911795</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01756608398864046</v>
+        <v>0.01833412499399856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02076962502906099</v>
+        <v>0.02074308396549895</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0242477499996312</v>
+        <v>0.02404291700804606</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3414,7 +3414,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02482474996941164</v>
+        <v>0.02499566599726677</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02276379195973277</v>
+        <v>0.02406916697509587</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3842,7 +3842,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02471716701984406</v>
+        <v>0.02521237498149276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02419145795283839</v>
+        <v>0.02323833300033584</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02319466701010242</v>
+        <v>0.02334737504133955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02121074998285621</v>
+        <v>0.02080679195933044</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4698,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0219158330000937</v>
+        <v>0.02236491697840393</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02151958300964907</v>
+        <v>0.02181083400500938</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02316970902029425</v>
+        <v>0.02480416698381305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01877462497213855</v>
+        <v>0.02122879197122529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01930408301996067</v>
+        <v>0.01913475000765175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02280908398097381</v>
+        <v>0.02317954105092213</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02254720800556242</v>
+        <v>0.02237441600300372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01857804198516533</v>
+        <v>0.01883974997326732</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01582733303075656</v>
+        <v>0.01579791697440669</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02214862499386072</v>
+        <v>0.02116016601212323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01897899998584762</v>
+        <v>0.01875008299248293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02079366601537913</v>
+        <v>0.02011566696455702</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02191616699565202</v>
+        <v>0.02255208301357925</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02141124999616295</v>
+        <v>0.02123150002444163</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02213858300819993</v>
+        <v>0.02282441698480397</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -7908,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02097908401628956</v>
+        <v>0.02055049996124581</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0209497920004651</v>
+        <v>0.02180812502047047</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02028662501834333</v>
+        <v>0.02069395803846419</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02301929204259068</v>
+        <v>0.02318829199066386</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01871475001098588</v>
+        <v>0.01813716697506607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -8978,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01889795798342675</v>
+        <v>0.0192385419504717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9192,7 +9192,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02177158300764859</v>
+        <v>0.02219904196681455</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02719833300216123</v>
+        <v>0.02697758300928399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02228191698668525</v>
+        <v>0.02160179201746359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02361233299598098</v>
+        <v>0.0231659589917399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02119599998695776</v>
+        <v>0.02043595799477771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02298770798370242</v>
+        <v>0.02237437502481043</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02658325002994388</v>
+        <v>0.02644891705131158</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0229863750282675</v>
+        <v>0.02201483299722895</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -10904,7 +10904,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02574675000505522</v>
+        <v>0.02470312500372529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11118,7 +11118,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01962199999252334</v>
+        <v>0.01975787500850856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11332,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02411025000037625</v>
+        <v>0.0231932089664042</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02132966701174155</v>
+        <v>0.02045887499116361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01805799995781854</v>
+        <v>0.01730191597016528</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02581687504425645</v>
+        <v>0.0250022909604013</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02035025000805035</v>
+        <v>0.01942799997050315</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02313479199074209</v>
+        <v>0.02266104199225083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02394983300473541</v>
+        <v>0.02334541600430384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01920141698792577</v>
+        <v>0.01950645894976333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02192566700978205</v>
+        <v>0.022541958023794</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0207838750211522</v>
+        <v>0.0209500000346452</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02363608300220221</v>
+        <v>0.02280104201054201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02214041701517999</v>
+        <v>0.02121824998175725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02520279202144593</v>
+        <v>0.02369237499078736</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02308645902667195</v>
+        <v>0.02225304098101333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02163783396827057</v>
+        <v>0.0207660419982858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02069391700206324</v>
+        <v>0.0204757500323467</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01783550000982359</v>
+        <v>0.01754233299288899</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01782000000821427</v>
+        <v>0.01727716595632955</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15184,7 +15184,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02389599999878556</v>
+        <v>0.02715641696704552</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02301162498770282</v>
+        <v>0.02248120802687481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15612,7 +15612,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02160929096862674</v>
+        <v>0.02020337496651337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02238254103576764</v>
+        <v>0.02122812496963888</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02262879197951406</v>
+        <v>0.02224075002595782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01792274997569621</v>
+        <v>0.01761875004740432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01948766701389104</v>
+        <v>0.01915200002258644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0230927910306491</v>
+        <v>0.02327070897445083</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02011241699801758</v>
+        <v>0.01949195901397616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02072425000369549</v>
+        <v>0.02060108399018645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02383183303754777</v>
+        <v>0.02375858399318531</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02577712503261864</v>
+        <v>0.02537591703003272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01987350004492328</v>
+        <v>0.01919525000266731</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02084308303892612</v>
+        <v>0.0201390830334276</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02330608404008672</v>
+        <v>0.02321700000902638</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02708154200809076</v>
+        <v>0.02674670802662149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02207716699922457</v>
+        <v>0.02158229099586606</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -18822,7 +18822,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02187208301620558</v>
+        <v>0.02184595802100375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01924824999878183</v>
+        <v>0.01886820903746411</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0210511659970507</v>
+        <v>0.02104237501043826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02761712501524016</v>
+        <v>0.02783216704847291</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02454629103885964</v>
+        <v>0.02464762498857453</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01717033400200307</v>
+        <v>0.01706112502142787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02321916696382686</v>
+        <v>0.02221516601275653</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02176604204578325</v>
+        <v>0.02103362500201911</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0201610840158537</v>
+        <v>0.01948462502332404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01815995801007375</v>
+        <v>0.01756116701290011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01874537504045293</v>
+        <v>0.01786770904436707</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21176,7 +21176,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02785629098070785</v>
+        <v>0.02686962502775714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.025851208018139</v>
+        <v>0.02417845802847296</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02232058299705386</v>
+        <v>0.02144162502372637</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.02167058299528435</v>
+        <v>0.02020958397770301</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
